--- a/out/LSTM-S4_repeat_5_000008.xlsx
+++ b/out/LSTM-S4_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.045076465039656</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.045076465039656</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.645076465039656</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.645076465039656</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001238376301070675</v>
+        <v>-8.908517028472852e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1422656517837551</v>
+        <v>-0.1023417502729988</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1424978587850047</v>
+        <v>-0.1025097581408063</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3896713217752817</v>
+        <v>0.2837880463890378</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6375934824515278</v>
+        <v>0.4656112180782985</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02776399986268727</v>
+        <v>0.02021983872223807</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3028246438486886</v>
+        <v>0.2218076219583314</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04868859597820894</v>
+        <v>0.03545857947315587</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3724287541934116</v>
+        <v>0.272498451292105</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05915089403596992</v>
+        <v>0.04307829822141423</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4420376810263274</v>
+        <v>0.3231928376953367</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01565280859923878</v>
+        <v>0.0113993390061749</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4141165901708498</v>
+        <v>0.3028586413121533</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008695383015589458</v>
+        <v>0.006331256169607655</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4158400493177867</v>
+        <v>0.3041124318635659</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01827053779231803</v>
+        <v>0.01330510269712677</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4436977541478302</v>
+        <v>0.3243998215040392</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007175455518560654</v>
+        <v>0.005224415909789999</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4397612374574552</v>
+        <v>0.32153155804156</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005107707740653786</v>
+        <v>0.003719134956839246</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4427999316114926</v>
+        <v>0.3237432331153297</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002007394756689171</v>
+        <v>0.001460164603554397</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4417026667850106</v>
+        <v>0.3229428877413782</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001137187156754017</v>
+        <v>0.0008273631101851133</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4419686574461174</v>
+        <v>0.3231352369128624</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004306909845829187</v>
+        <v>0.0003120796922840649</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4416903965264517</v>
+        <v>0.3229313677799522</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001986776820319919</v>
+        <v>0.0001436296598611833</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4416578526979338</v>
+        <v>0.322906321862346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.008125237491961e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4415980647802064</v>
+        <v>0.3228615570089519</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.69413445763141e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4415622720390167</v>
+        <v>0.3228340416141267</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4415572549122497</v>
+        <v>0.3228290289552121</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4415531274111709</v>
+        <v>0.3228246473696513</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4415503262652932</v>
+        <v>0.3228212970148586</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4415448825202868</v>
+        <v>0.3228159276878708</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4415388897868565</v>
+        <v>0.3228099349544404</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4415335219982781</v>
+        <v>0.3228045671658621</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4415335587467698</v>
+        <v>0.3228046039143538</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4415336689922453</v>
+        <v>0.3228047141598293</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4415337424892289</v>
+        <v>0.3228047876568129</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4415339262316881</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4415354696683446</v>
+        <v>0.3228065148359286</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4415369396080177</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4415381890567397</v>
+        <v>0.3228092342243237</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.441539548750937</v>
+        <v>0.322810593918521</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4415373438414277</v>
+        <v>0.3228083890090117</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4415369396080177</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4415360943927057</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.441536645620083</v>
+        <v>0.322807690787667</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4415363148836566</v>
+        <v>0.3228073600512406</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4415360208957221</v>
+        <v>0.3228070660633061</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4415360943927057</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4415356534108038</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4415355431653282</v>
+        <v>0.3228065883329122</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4415355064168365</v>
+        <v>0.3228065515844205</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4415356534108038</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4415351756804101</v>
+        <v>0.3228062208479941</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4415361311411974</v>
+        <v>0.3228071763087814</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4415360943927057</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4415357636562793</v>
+        <v>0.3228068088238633</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4415362046381813</v>
+        <v>0.3228072498057653</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4415355799138201</v>
+        <v>0.3228066250814041</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4415353961713609</v>
+        <v>0.3228064413389449</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4415349919379509</v>
+        <v>0.3228060371055349</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.441534146722639</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4415341099741473</v>
+        <v>0.3228051551417312</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4415342569681145</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4415341834711309</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4415342569681145</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4415342937166065</v>
+        <v>0.3228053388841904</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4415341834711309</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4415346244530329</v>
+        <v>0.3228056696206169</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4415345142075573</v>
+        <v>0.3228055593751413</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4415344774590654</v>
+        <v>0.3228055226266494</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4415344039620818</v>
+        <v>0.3228054491296657</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4415343672135901</v>
+        <v>0.3228054123811741</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.441534146722639</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4415340732256554</v>
+        <v>0.3228051183932393</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4415339997286717</v>
+        <v>0.3228050448962557</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4415340364771637</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4415339262316881</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4415340364771637</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4415343304650982</v>
+        <v>0.3228053756326821</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_5_000008.xlsx
+++ b/out/LSTM-S4_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001238376301070675</v>
+        <v>-0.000120125918806647</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1422656517837551</v>
+        <v>-0.1380016083993995</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1423894894138622</v>
+        <v>-0.1381217343182062</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1424978587850047</v>
+        <v>-0.1382271048633272</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3896713217752817</v>
+        <v>0.3788884831033206</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6375934824515278</v>
+        <v>0.6202773411052935</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02776399986268727</v>
+        <v>0.02699568828496527</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3028246438486886</v>
+        <v>0.2947725291924009</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04868859597820894</v>
+        <v>0.04734123925086071</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3724287541934116</v>
+        <v>0.3624504940635643</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05915089403596992</v>
+        <v>0.05751401473380858</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.045076465039656</v>
+        <v>0.2418255450559278</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4420376810263274</v>
+        <v>0.430133147221213</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01565280859923878</v>
+        <v>0.0152198143366104</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.2418255450559278</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4141165901708498</v>
+        <v>0.4029847066228345</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008695383015589458</v>
+        <v>0.008454347736599694</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.045076465039656</v>
+        <v>0.2418255450559278</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4158400493177867</v>
+        <v>0.4046603173122953</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01827053779231803</v>
+        <v>0.01776512019968243</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4436977541478302</v>
+        <v>0.4317474274327087</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007175455518560654</v>
+        <v>0.006976839444173076</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.645076465039656</v>
+        <v>0.2418255450559279</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4397612374574552</v>
+        <v>0.4279196590535536</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005107707740653786</v>
+        <v>0.004966263059569573</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.3986870573439083</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4427999316114926</v>
+        <v>0.4308741626767668</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002007394756689171</v>
+        <v>0.001951721217536502</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4417026667850106</v>
+        <v>0.4298071055365223</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001137187156754017</v>
+        <v>0.001106358893413828</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4419686574461174</v>
+        <v>0.4300656032265967</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004306909845829187</v>
+        <v>0.0004177729230454198</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4416903965264517</v>
+        <v>0.4297950768977981</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001986776820319919</v>
+        <v>0.000193172879814911</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4416578526979338</v>
+        <v>0.4297632755106729</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.008125237491961e-05</v>
+        <v>6.76592764918577e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4415980647802064</v>
+        <v>0.4297049609571956</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.69413445763141e-05</v>
+        <v>1.64643588246551e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4415622720390167</v>
+        <v>0.4296698304335009</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4415572549122497</v>
+        <v>0.429664813306734</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4415531274111709</v>
+        <v>0.4296606498459033</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4415503262652932</v>
+        <v>0.4296578487000256</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4415448825202868</v>
+        <v>0.4296524049550192</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4415388897868565</v>
+        <v>0.4296464122215889</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4415335219982781</v>
+        <v>0.4296410444330105</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4415335587467698</v>
+        <v>0.4296410811815022</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4415336689922453</v>
+        <v>0.4296411914269778</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4415337424892289</v>
+        <v>0.4296412649239614</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4415339262316881</v>
+        <v>0.4296414486664205</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4415354696683446</v>
+        <v>0.429642992103077</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4415369396080177</v>
+        <v>0.4296444620427501</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4415381890567397</v>
+        <v>0.4296457114914721</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.441539548750937</v>
+        <v>0.4296470711856694</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4415373438414277</v>
+        <v>0.4296448662761601</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4415369396080177</v>
+        <v>0.4296444620427501</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4415360943927057</v>
+        <v>0.4296436168274381</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.441536645620083</v>
+        <v>0.4296441680548154</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4415363148836566</v>
+        <v>0.429643837318389</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4415360208957221</v>
+        <v>0.4296435433304545</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4415360943927057</v>
+        <v>0.4296436168274381</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4415356534108038</v>
+        <v>0.4296431758455362</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4415355431653282</v>
+        <v>0.4296430656000606</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4415355064168365</v>
+        <v>0.4296430288515689</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4415356534108038</v>
+        <v>0.4296431758455362</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4415351756804101</v>
+        <v>0.4296426981151426</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4415361311411974</v>
+        <v>0.4296436535759298</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4415360943927057</v>
+        <v>0.4296436168274381</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4415357636562793</v>
+        <v>0.4296432860910117</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4415362046381813</v>
+        <v>0.4296437270729137</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4415355799138201</v>
+        <v>0.4296431023485526</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4415353961713609</v>
+        <v>0.4296429186060934</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4415349919379509</v>
+        <v>0.4296425143726834</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.441534146722639</v>
+        <v>0.4296416691573714</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4415341099741473</v>
+        <v>0.4296416324088797</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4415342569681145</v>
+        <v>0.4296417794028469</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4415341834711309</v>
+        <v>0.4296417059058633</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4415342569681145</v>
+        <v>0.4296417794028469</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4415342937166065</v>
+        <v>0.4296418161513388</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4415341834711309</v>
+        <v>0.4296417059058633</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4415346244530329</v>
+        <v>0.4296421468877653</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4415345142075573</v>
+        <v>0.4296420366422897</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4415344774590654</v>
+        <v>0.4296419998937978</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4415344039620818</v>
+        <v>0.4296419263968142</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4415343672135901</v>
+        <v>0.4296418896483225</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.441534146722639</v>
+        <v>0.4296416691573714</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4415340732256554</v>
+        <v>0.4296415956603878</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4415339997286717</v>
+        <v>0.4296415221634042</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4415340364771637</v>
+        <v>0.4296415589118961</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4415339262316881</v>
+        <v>0.4296414486664205</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4415340364771637</v>
+        <v>0.4296415589118961</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4415343304650982</v>
+        <v>0.4296418528998305</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_5_000008.xlsx
+++ b/out/LSTM-S4_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.004028875380754471</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.002753276377916336</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.23</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.003049630671739578</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003409285098314285</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002673953771591187</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001928187906742096</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.001892432570457458</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.082338147455764</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.001974854618310928</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.082338147455764</v>
+        <v>0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001986172050237656</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.002037405967712402</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.002317048609256744</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002611808478832245</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.002815883606672287</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.002858266234397888</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003265146166086197</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.003196191042661667</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002944972366094589</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002771548926830292</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002802260220050812</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.003008056432008743</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003139879554510117</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.00327729806303978</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00352780893445015</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.003950361162424088</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004156328737735748</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.004186544567346573</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.004134491086006165</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.004321638494729996</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.004476282745599747</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.004527058452367783</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.005197983235120773</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.004967298358678818</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.00472714751958847</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.004617232829332352</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.004527375102043152</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.004628367722034454</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.004432659596204758</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.004256892949342728</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004491467028856277</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004667997360229492</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.004661612212657928</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.004876527935266495</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.005381327122449875</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.00549866259098053</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000120125918806647</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1380016083993995</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.004204180091619492</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.003485646098852158</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.002544771879911423</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.002005022019147873</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.001572243869304657</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.00128314271569252</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001334056258201599</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001813367009162903</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.002045039087533951</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.00215737521648407</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.002134628593921661</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.001881606876850128</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.001647625118494034</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1381217343182062</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.001801412552595139</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1382271048633272</v>
+        <v>-0.1302574926734896</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3788884831033206</v>
+        <v>0.2338688282598552</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001190338283777237</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6202773411052935</v>
+        <v>0.3379292005604627</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02699568828496527</v>
+        <v>0.01666306832510367</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0008580312132835388</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2947725291924009</v>
+        <v>0.1370114310152538</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04734123925086071</v>
+        <v>0.02922147270272843</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001000579446554184</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3624504940635643</v>
+        <v>0.1787856740458205</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05751401473380858</v>
+        <v>0.03550063830527529</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.000539686530828476</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2418255450559278</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.430133147221213</v>
+        <v>0.220562697515015</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0152198143366104</v>
+        <v>0.009393237161945765</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0001337416470050812</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2418255450559278</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4029847066228345</v>
+        <v>0.2038044951955106</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008454347736599694</v>
+        <v>0.005216697299636718</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0004738308489322662</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2418255450559278</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4046603173122953</v>
+        <v>0.2048368622222175</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01776512019968243</v>
+        <v>0.01096369609643938</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0007300823926925659</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4317474274327087</v>
+        <v>0.2215547841622636</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006976839444173076</v>
+        <v>0.004303999955310981</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0001874864101409912</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2418255450559279</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4279196590535536</v>
+        <v>0.2191901455519372</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004966263059569573</v>
+        <v>0.003063659605473376</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001054376363754272</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3986870573439083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4308741626767668</v>
+        <v>0.2210121838641879</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001951721217536502</v>
+        <v>0.001203523166972579</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001766566187143326</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4298071055365223</v>
+        <v>0.2203514560409817</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001106358893413828</v>
+        <v>0.0006809288593192138</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002640657126903534</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4300656032265967</v>
+        <v>0.220509086376742</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004177729230454198</v>
+        <v>0.0002557099692113423</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003504090011119843</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4297950768977981</v>
+        <v>0.2203402042714309</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000193172879814911</v>
+        <v>0.0001172066092191951</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.004320170730352402</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4297632755106729</v>
+        <v>0.2203186485755267</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.76592764918577e-05</v>
+        <v>4.021021648382256e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004877194762229919</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4297049609571956</v>
+        <v>0.220280658001411</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.64643588246551e-05</v>
+        <v>8.355601046452064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.004864305257797241</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4296698304335009</v>
+        <v>0.2202571159115553</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.004714205861091614</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.429664813306734</v>
+        <v>0.2202521054865667</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004429452121257782</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4296606498459033</v>
+        <v>0.2202476144442705</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.908363659633048e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004471093416213989</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4296578487000256</v>
+        <v>0.2202438976137908</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004535354673862457</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4296524049550192</v>
+        <v>0.2202386017837867</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004567388445138931</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4296464122215889</v>
+        <v>0.220232939786783</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.004522278904914856</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4296410444330105</v>
+        <v>0.2202327560443238</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004385355859994888</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4296410811815022</v>
+        <v>0.2202327927928155</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004127118736505508</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4296411914269778</v>
+        <v>0.220232903038291</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004021383821964264</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4296412649239614</v>
+        <v>0.2202329765352747</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003521978855133057</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4296414486664205</v>
+        <v>0.2202331602777338</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002557698637247086</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.429642992103077</v>
+        <v>0.2202347037143903</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002802029252052307</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4296444620427501</v>
+        <v>0.2202361736540634</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003220736980438232</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4296457114914721</v>
+        <v>0.2202374231027854</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001956183463335037</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4296470711856694</v>
+        <v>0.2202387827969827</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003809858113527298</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4296448662761601</v>
+        <v>0.2202365778874734</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.005753356963396072</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4296444620427501</v>
+        <v>0.2202361736540634</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.00720011442899704</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4296436168274381</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008550658822059631</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4296441680548154</v>
+        <v>0.2202358796661286</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.009698700159788132</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.429643837318389</v>
+        <v>0.2202355489297023</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01018554344773293</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4296435433304545</v>
+        <v>0.2202352549417678</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0106714554131031</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4296436168274381</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01075107231736183</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4296431758455362</v>
+        <v>0.2202348874568494</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01044848933815956</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4296430656000606</v>
+        <v>0.2202347772113739</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.009973715990781784</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4296430288515689</v>
+        <v>0.2202347404628822</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.009832940995693207</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4296431758455362</v>
+        <v>0.2202348874568494</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.008591704070568085</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4296426981151426</v>
+        <v>0.2202344097264558</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.007899876683950424</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4296436535759298</v>
+        <v>0.2202353651872431</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.009035367518663406</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4296436168274381</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01015149801969528</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4296432860910117</v>
+        <v>0.220234997702325</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01071063429117203</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4296437270729137</v>
+        <v>0.220235438684227</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01098020374774933</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4296431023485526</v>
+        <v>0.2202348139598658</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01131791621446609</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4296429186060934</v>
+        <v>0.2202346302174067</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01154251769185066</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4296425143726834</v>
+        <v>0.2202342259839966</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01130616664886475</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4296416691573714</v>
+        <v>0.2202333807686847</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01050826907157898</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4296416324088797</v>
+        <v>0.220233344020193</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.009818185120820999</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4296417794028469</v>
+        <v>0.2202334910141602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.009205207228660583</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4296417059058633</v>
+        <v>0.2202334175171766</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.008070893585681915</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4296417794028469</v>
+        <v>0.2202334910141602</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.007997486740350723</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4296418161513388</v>
+        <v>0.2202335277626521</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.007572278380393982</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4296417059058633</v>
+        <v>0.2202334175171766</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.007763039320707321</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4296421468877653</v>
+        <v>0.2202338584990785</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.007707763463258743</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4296420366422897</v>
+        <v>0.220233748253603</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.007658161222934723</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4296419998937978</v>
+        <v>0.2202337115051111</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.007794857025146484</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4296419263968142</v>
+        <v>0.2202336380081275</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.007797099649906158</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4296418896483225</v>
+        <v>0.2202336012596358</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.007894128561019897</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4296416691573714</v>
+        <v>0.2202333807686847</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.007550783455371857</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4296415956603878</v>
+        <v>0.220233307271701</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.007043510675430298</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4296415221634042</v>
+        <v>0.2202332337747174</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.006679881364107132</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4296415589118961</v>
+        <v>0.2202332705232093</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.006103858351707458</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4296414486664205</v>
+        <v>0.2202331602777338</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005312297493219376</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4296415589118961</v>
+        <v>0.2202332705232093</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.005046989768743515</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4296418528998305</v>
+        <v>0.2202335645111438</v>
       </c>
     </row>
   </sheetData>
